--- a/listsorter.xlsx
+++ b/listsorter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f75adbc1b1328d64/Documents/GitHub/us-filament-cos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{43F61E5D-CE72-4242-B668-B64B7F72F136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B744E806-6279-4A1B-92B6-ABB4A79BCA2D}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{43F61E5D-CE72-4242-B668-B64B7F72F136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED0672F-4196-49C1-99D0-EE66AB2F20B5}"/>
   <bookViews>
-    <workbookView xWindow="-375" yWindow="8220" windowWidth="38700" windowHeight="12870" xr2:uid="{9B57F534-A7CF-4819-AB34-56834F09031D}"/>
+    <workbookView xWindow="1830" yWindow="5310" windowWidth="38700" windowHeight="15345" xr2:uid="{9B57F534-A7CF-4819-AB34-56834F09031D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="105">
   <si>
     <t>ZYLtech Engineering LLC</t>
   </si>
@@ -345,6 +345,15 @@
   </si>
   <si>
     <t>China</t>
+  </si>
+  <si>
+    <t>Dancyn 3D</t>
+  </si>
+  <si>
+    <t>https://www.dancyn3dprints.com/</t>
+  </si>
+  <si>
+    <t>Whippany, NJ</t>
   </si>
 </sst>
 </file>
@@ -727,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5A59DF-FE25-4F2F-AF48-72493BDAE325}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
@@ -833,7 +842,7 @@
         <v>82</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R26" si="0">"| "&amp;$C3&amp;" | "&amp;$D3&amp;" | "&amp;$E3&amp;" | "&amp;$F3&amp;" | "&amp;$G3&amp;" | "&amp;$H3&amp;" | "&amp;$I3&amp;" | "&amp;$J3&amp;" | "&amp;$K3&amp;" | "&amp;$L3&amp;" | "&amp;$M3&amp;" | "&amp;$N3&amp;" | "&amp;$O3&amp;" | "&amp;$P3&amp;" |"</f>
+        <f t="shared" ref="R3:R27" si="0">"| "&amp;$C3&amp;" | "&amp;$D3&amp;" | "&amp;$E3&amp;" | "&amp;$F3&amp;" | "&amp;$G3&amp;" | "&amp;$H3&amp;" | "&amp;$I3&amp;" | "&amp;$J3&amp;" | "&amp;$K3&amp;" | "&amp;$L3&amp;" | "&amp;$M3&amp;" | "&amp;$N3&amp;" | "&amp;$O3&amp;" | "&amp;$P3&amp;" |"</f>
         <v>| [3D-Fuel](https://www.3dfuel.com) | Fargo, North Dakota |  |  | X | X |  | X |  |  |  |  |  |  |</v>
       </c>
     </row>
@@ -1024,17 +1033,17 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="C9" t="str">
         <f>"["&amp;A9&amp;"]"&amp;"("&amp;B9&amp;")"</f>
-        <v>[FilaCube](https://www.filacube.com/)</v>
+        <v>[Dancyn 3D](https://www.dancyn3dprints.com/)</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
         <v>82</v>
@@ -1042,30 +1051,24 @@
       <c r="H9" t="s">
         <v>82</v>
       </c>
-      <c r="J9" t="s">
-        <v>82</v>
-      </c>
-      <c r="M9" t="s">
-        <v>82</v>
-      </c>
       <c r="R9" t="str">
         <f t="shared" si="0"/>
-        <v>| [FilaCube](https://www.filacube.com/) | Houston/Katy, Texas |  |  | X | X |  | X |  |  | X |  |  |  |</v>
+        <v>| [Dancyn 3D](https://www.dancyn3dprints.com/) | Whippany, NJ |  |  | X | X |  |  |  |  |  |  |  |  |</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C10" t="str">
         <f>"["&amp;A10&amp;"]"&amp;"("&amp;B10&amp;")"</f>
-        <v>[Filamatrix](https://filamatrix.com/)</v>
+        <v>[FilaCube](https://www.filacube.com/)</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
         <v>82</v>
@@ -1073,39 +1076,30 @@
       <c r="H10" t="s">
         <v>82</v>
       </c>
-      <c r="I10" t="s">
-        <v>82</v>
-      </c>
       <c r="J10" t="s">
         <v>82</v>
       </c>
-      <c r="L10" t="s">
-        <v>82</v>
-      </c>
-      <c r="N10" t="s">
-        <v>82</v>
-      </c>
-      <c r="P10" t="s">
-        <v>87</v>
+      <c r="M10" t="s">
+        <v>82</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="0"/>
-        <v>| [Filamatrix](https://filamatrix.com/) | Chester, Virgina |  |  | X | X | X | X |  | X |  | X |  | Kevlar Composite |</v>
+        <v>| [FilaCube](https://www.filacube.com/) | Houston/Katy, Texas |  |  | X | X |  | X |  |  | X |  |  |  |</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C11" t="str">
         <f>"["&amp;A11&amp;"]"&amp;"("&amp;B11&amp;")"</f>
-        <v>[Fusion Filaments](https://www.fusionfilaments.com)</v>
+        <v>[Filamatrix](https://filamatrix.com/)</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
         <v>82</v>
@@ -1119,86 +1113,89 @@
       <c r="J11" t="s">
         <v>82</v>
       </c>
-      <c r="O11" t="s">
-        <v>82</v>
+      <c r="L11" t="s">
+        <v>82</v>
+      </c>
+      <c r="N11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P11" t="s">
+        <v>87</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="0"/>
-        <v>| [Fusion Filaments](https://www.fusionfilaments.com) | Maryland Heights, Missouri |  |  | X | X | X | X |  |  |  |  | X |  |</v>
+        <v>| [Filamatrix](https://filamatrix.com/) | Chester, Virgina |  |  | X | X | X | X |  | X |  | X |  | Kevlar Composite |</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C12" t="str">
         <f>"["&amp;A12&amp;"]"&amp;"("&amp;B12&amp;")"</f>
-        <v>[GreenGate3D](https://greengate3d.com)</v>
+        <v>[Fusion Filaments](https://www.fusionfilaments.com)</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
       </c>
       <c r="H12" t="s">
         <v>82</v>
       </c>
+      <c r="I12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" t="s">
+        <v>82</v>
+      </c>
+      <c r="O12" t="s">
+        <v>82</v>
+      </c>
       <c r="R12" t="str">
         <f t="shared" si="0"/>
-        <v>| [GreenGate3D](https://greengate3d.com) | Bohemia/Long Island, New York |  |  |  | X |  |  |  |  |  |  |  |  |</v>
+        <v>| [Fusion Filaments](https://www.fusionfilaments.com) | Maryland Heights, Missouri |  |  | X | X | X | X |  |  |  |  | X |  |</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" t="str">
         <f>"["&amp;A13&amp;"]"&amp;"("&amp;B13&amp;")"</f>
-        <v>[IC3D](https://www.ic3dprinters.com)</v>
+        <v>[GreenGate3D](https://greengate3d.com)</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H13" t="s">
         <v>82</v>
       </c>
-      <c r="J13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" t="s">
-        <v>82</v>
-      </c>
-      <c r="N13" t="s">
-        <v>82</v>
-      </c>
       <c r="R13" t="str">
         <f t="shared" si="0"/>
-        <v>| [IC3D](https://www.ic3dprinters.com) | Columbus, Ohio |  |  | X | X |  | X |  |  | X | X |  |  |</v>
+        <v>| [GreenGate3D](https://greengate3d.com) | Bohemia/Long Island, New York |  |  |  | X |  |  |  |  |  |  |  |  |</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="C14" t="str">
         <f>"["&amp;A14&amp;"]"&amp;"("&amp;B14&amp;")"</f>
-        <v>[Lumas Polymers](https://lumaspolymers.com/)</v>
+        <v>[IC3D](https://www.ic3dprinters.com)</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
         <v>82</v>
@@ -1209,39 +1206,33 @@
       <c r="J14" t="s">
         <v>82</v>
       </c>
-      <c r="K14" t="s">
-        <v>82</v>
-      </c>
-      <c r="L14" t="s">
-        <v>82</v>
-      </c>
       <c r="M14" t="s">
         <v>82</v>
       </c>
       <c r="N14" t="s">
         <v>82</v>
       </c>
-      <c r="P14" t="s">
-        <v>91</v>
-      </c>
       <c r="R14" t="str">
         <f t="shared" si="0"/>
-        <v>| [Lumas Polymers](https://lumaspolymers.com/) | Sioux Fall, South Dakota | Chaska, Minnesota |  | X | X |  | X | X | X | X | X |  | TPE |</v>
+        <v>| [IC3D](https://www.ic3dprinters.com) | Columbus, Ohio |  |  | X | X |  | X |  |  | X | X |  |  |</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="C15" t="str">
         <f>"["&amp;A15&amp;"]"&amp;"("&amp;B15&amp;")"</f>
-        <v>[MatterHackers ProSeries](https://www.matterhackers.com/store/c/pro-series-filament)</v>
+        <v>[Lumas Polymers](https://lumaspolymers.com/)</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
       </c>
       <c r="G15" t="s">
         <v>82</v>
@@ -1252,33 +1243,39 @@
       <c r="J15" t="s">
         <v>82</v>
       </c>
+      <c r="K15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L15" t="s">
+        <v>82</v>
+      </c>
       <c r="M15" t="s">
         <v>82</v>
       </c>
       <c r="N15" t="s">
         <v>82</v>
       </c>
+      <c r="P15" t="s">
+        <v>91</v>
+      </c>
       <c r="R15" t="str">
         <f t="shared" si="0"/>
-        <v>| [MatterHackers ProSeries](https://www.matterhackers.com/store/c/pro-series-filament) | Lake Forest, California |  |  | X | X |  | X |  |  | X | X |  |  |</v>
+        <v>| [Lumas Polymers](https://lumaspolymers.com/) | Sioux Fall, South Dakota | Chaska, Minnesota |  | X | X |  | X | X | X | X | X |  | TPE |</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C16" t="str">
         <f>"["&amp;A16&amp;"]"&amp;"("&amp;B16&amp;")"</f>
-        <v>[Numakers](https://numakers.com)</v>
+        <v>[MatterHackers ProSeries](https://www.matterhackers.com/store/c/pro-series-filament)</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s">
         <v>82</v>
@@ -1286,33 +1283,36 @@
       <c r="H16" t="s">
         <v>82</v>
       </c>
-      <c r="I16" t="s">
-        <v>82</v>
-      </c>
       <c r="J16" t="s">
         <v>82</v>
       </c>
       <c r="M16" t="s">
         <v>82</v>
       </c>
+      <c r="N16" t="s">
+        <v>82</v>
+      </c>
       <c r="R16" t="str">
         <f t="shared" si="0"/>
-        <v>| [Numakers](https://numakers.com) | Richmond, Virgina | India |  | X | X | X | X |  |  | X |  |  |  |</v>
+        <v>| [MatterHackers ProSeries](https://www.matterhackers.com/store/c/pro-series-filament) | Lake Forest, California |  |  | X | X |  | X |  |  | X | X |  |  |</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="C17" t="str">
         <f>"["&amp;A17&amp;"]"&amp;"("&amp;B17&amp;")"</f>
-        <v>[Paramount3D](https://www.paramount-3d.com/)</v>
+        <v>[Numakers](https://numakers.com)</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
       </c>
       <c r="G17" t="s">
         <v>82</v>
@@ -1329,27 +1329,24 @@
       <c r="M17" t="s">
         <v>82</v>
       </c>
-      <c r="P17" t="s">
-        <v>92</v>
-      </c>
       <c r="R17" t="str">
         <f t="shared" si="0"/>
-        <v>| [Paramount3D](https://www.paramount-3d.com/) | Bensenville/Wood Dale, Illinois |  |  | X | X | X | X |  |  | X |  |  | FlexPLA, PVA |</v>
+        <v>| [Numakers](https://numakers.com) | Richmond, Virgina | India |  | X | X | X | X |  |  | X |  |  |  |</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="C18" t="str">
         <f>"["&amp;A18&amp;"]"&amp;"("&amp;B18&amp;")"</f>
-        <v>[Polar Filament](https://polarfilament.com)</v>
+        <v>[Paramount3D](https://www.paramount-3d.com/)</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
         <v>82</v>
@@ -1357,24 +1354,36 @@
       <c r="H18" t="s">
         <v>82</v>
       </c>
+      <c r="I18" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" t="s">
+        <v>82</v>
+      </c>
+      <c r="M18" t="s">
+        <v>82</v>
+      </c>
+      <c r="P18" t="s">
+        <v>92</v>
+      </c>
       <c r="R18" t="str">
         <f t="shared" si="0"/>
-        <v>| [Polar Filament](https://polarfilament.com) | Brighton, Michigan |  |  | X | X |  |  |  |  |  |  |  |  |</v>
+        <v>| [Paramount3D](https://www.paramount-3d.com/) | Bensenville/Wood Dale, Illinois |  |  | X | X | X | X |  |  | X |  |  | FlexPLA, PVA |</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C19" t="str">
         <f>"["&amp;A19&amp;"]"&amp;"("&amp;B19&amp;")"</f>
-        <v>[Printed Solid](https://www.printedsolid.com)</v>
+        <v>[Polar Filament](https://polarfilament.com)</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s">
         <v>82</v>
@@ -1382,30 +1391,24 @@
       <c r="H19" t="s">
         <v>82</v>
       </c>
-      <c r="I19" t="s">
-        <v>82</v>
-      </c>
-      <c r="J19" t="s">
-        <v>82</v>
-      </c>
       <c r="R19" t="str">
         <f t="shared" si="0"/>
-        <v>| [Printed Solid](https://www.printedsolid.com) | Newark, Delaware |  |  | X | X | X | X |  |  |  |  |  |  |</v>
+        <v>| [Polar Filament](https://polarfilament.com) | Brighton, Michigan |  |  | X | X |  |  |  |  |  |  |  |  |</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C20" t="str">
         <f>"["&amp;A20&amp;"]"&amp;"("&amp;B20&amp;")"</f>
-        <v>[Protopasta](https://proto-pasta.com/)</v>
+        <v>[Printed Solid](https://www.printedsolid.com)</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
         <v>82</v>
@@ -1413,27 +1416,30 @@
       <c r="H20" t="s">
         <v>82</v>
       </c>
-      <c r="K20" t="s">
+      <c r="I20" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s">
         <v>82</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="0"/>
-        <v>| [Protopasta](https://proto-pasta.com/) | Vancouver, Washington |  |  | X | X |  |  | X |  |  |  |  |  |</v>
+        <v>| [Printed Solid](https://www.printedsolid.com) | Newark, Delaware |  |  | X | X | X | X |  |  |  |  |  |  |</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C21" t="str">
         <f>"["&amp;A21&amp;"]"&amp;"("&amp;B21&amp;")"</f>
-        <v>[Push Plastic](https://www.pushplastic.com)</v>
+        <v>[Protopasta](https://proto-pasta.com/)</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
         <v>82</v>
@@ -1441,110 +1447,101 @@
       <c r="H21" t="s">
         <v>82</v>
       </c>
-      <c r="J21" t="s">
-        <v>82</v>
-      </c>
       <c r="K21" t="s">
         <v>82</v>
       </c>
-      <c r="L21" t="s">
-        <v>82</v>
-      </c>
-      <c r="M21" t="s">
-        <v>82</v>
-      </c>
-      <c r="N21" t="s">
-        <v>82</v>
-      </c>
       <c r="R21" t="str">
         <f t="shared" si="0"/>
-        <v>| [Push Plastic](https://www.pushplastic.com) | Springdale, Arkansas |  |  | X | X |  | X | X | X | X | X |  |  |</v>
+        <v>| [Protopasta](https://proto-pasta.com/) | Vancouver, Washington |  |  | X | X |  |  | X |  |  |  |  |  |</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C22" t="str">
         <f>"["&amp;A22&amp;"]"&amp;"("&amp;B22&amp;")"</f>
-        <v>[Tangled](https://www.tangledfilament.com/)</v>
+        <v>[Push Plastic](https://www.pushplastic.com)</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G22" t="s">
         <v>82</v>
       </c>
-      <c r="O22" t="s">
+      <c r="H22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22" t="s">
+        <v>82</v>
+      </c>
+      <c r="M22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" t="s">
         <v>82</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="0"/>
-        <v>| [Tangled](https://www.tangledfilament.com/) | Nampa/Boise, Idaho |  |  | X |  |  |  |  |  |  |  | X |  |</v>
+        <v>| [Push Plastic](https://www.pushplastic.com) | Springdale, Arkansas |  |  | X | X |  | X | X | X | X | X |  |  |</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C23" t="str">
         <f>"["&amp;A23&amp;"]"&amp;"("&amp;B23&amp;")"</f>
-        <v>[Toner Plastics (Village Plastics)](https://www.villageplastics.com/)</v>
+        <v>[Tangled](https://www.tangledfilament.com/)</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
         <v>82</v>
       </c>
-      <c r="H23" t="s">
-        <v>82</v>
-      </c>
-      <c r="I23" t="s">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" t="s">
-        <v>82</v>
-      </c>
-      <c r="M23" t="s">
-        <v>82</v>
-      </c>
-      <c r="P23" t="s">
-        <v>86</v>
+      <c r="O23" t="s">
+        <v>82</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="0"/>
-        <v>| [Toner Plastics (Village Plastics)](https://www.villageplastics.com/) | East Longmeadow, Massachusetts | Barberton, Ohio |  | X | X | X | X |  | X | X |  |  | HIPS |</v>
+        <v>| [Tangled](https://www.tangledfilament.com/) | Nampa/Boise, Idaho |  |  | X |  |  |  |  |  |  |  | X |  |</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
+        <v>44</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C24" t="str">
         <f>"["&amp;A24&amp;"]"&amp;"("&amp;B24&amp;")"</f>
-        <v>[Two Step Process (Luke's Laboratory)](https://www.lukeslabonline.com/)</v>
+        <v>[Toner Plastics (Village Plastics)](https://www.villageplastics.com/)</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>101</v>
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
       </c>
       <c r="I24" t="s">
         <v>82</v>
@@ -1552,113 +1549,151 @@
       <c r="J24" t="s">
         <v>82</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
+        <v>82</v>
+      </c>
+      <c r="M24" t="s">
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="0"/>
-        <v>| [Two Step Process (Luke's Laboratory)](https://www.lukeslabonline.com/) | Wrightstown, WI | China |  |  |  | X | X | X |  |  |  |  | PPC-CF, PET-CF, ABS-FR |</v>
+        <v>| [Toner Plastics (Village Plastics)](https://www.villageplastics.com/) | East Longmeadow, Massachusetts | Barberton, Ohio |  | X | X | X | X |  | X | X |  |  | HIPS |</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>42</v>
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
       </c>
       <c r="C25" t="str">
         <f>"["&amp;A25&amp;"]"&amp;"("&amp;B25&amp;")"</f>
-        <v>[Voxel](https://voxelpla.com/)</v>
+        <v>[Two Step Process (Luke's Laboratory)](https://www.lukeslabonline.com/)</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+      <c r="I25" t="s">
         <v>82</v>
       </c>
       <c r="J25" t="s">
         <v>82</v>
       </c>
-      <c r="M25" t="s">
-        <v>82</v>
+      <c r="K25" t="s">
+        <v>82</v>
+      </c>
+      <c r="P25" t="s">
+        <v>100</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="0"/>
-        <v>| [Voxel](https://voxelpla.com/) | Garden Grove, California |  |  | X | X |  | X |  |  | X |  |  |  |</v>
+        <v>| [Two Step Process (Luke's Laboratory)](https://www.lukeslabonline.com/) | Wrightstown, WI | China |  |  |  | X | X | X |  |  |  |  | PPC-CF, PET-CF, ABS-FR |</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C26" t="str">
         <f>"["&amp;A26&amp;"]"&amp;"("&amp;B26&amp;")"</f>
+        <v>[Voxel](https://voxelpla.com/)</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s">
+        <v>82</v>
+      </c>
+      <c r="M26" t="s">
+        <v>82</v>
+      </c>
+      <c r="R26" t="str">
+        <f t="shared" si="0"/>
+        <v>| [Voxel](https://voxelpla.com/) | Garden Grove, California |  |  | X | X |  | X |  |  | X |  |  |  |</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="str">
+        <f>"["&amp;A27&amp;"]"&amp;"("&amp;B27&amp;")"</f>
         <v>[ZYLtech Engineering LLC](https://www.zyltech.com)</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>58</v>
       </c>
-      <c r="G26" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" t="s">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s">
-        <v>82</v>
-      </c>
-      <c r="K26" t="s">
-        <v>82</v>
-      </c>
-      <c r="M26" t="s">
-        <v>82</v>
-      </c>
-      <c r="R26" t="str">
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" t="s">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s">
+        <v>82</v>
+      </c>
+      <c r="K27" t="s">
+        <v>82</v>
+      </c>
+      <c r="M27" t="s">
+        <v>82</v>
+      </c>
+      <c r="R27" t="str">
         <f t="shared" si="0"/>
         <v>| [ZYLtech Engineering LLC](https://www.zyltech.com) | Houston/Spring, Texas |  |  | X | X |  | X | X |  | X |  |  |  |</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P26">
-    <sortCondition ref="C2:C26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P27">
+    <sortCondition ref="A2:A27"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B26" r:id="rId1" xr:uid="{AD849A97-182F-461A-A5F7-8599BDB61E47}"/>
-    <hyperlink ref="B18" r:id="rId2" xr:uid="{D9F0C2C7-381A-4218-B772-BD3F900BF8D2}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{FB56925B-0B62-44BA-927F-C2AC4732FB38}"/>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{AD849A97-182F-461A-A5F7-8599BDB61E47}"/>
+    <hyperlink ref="B19" r:id="rId2" xr:uid="{D9F0C2C7-381A-4218-B772-BD3F900BF8D2}"/>
+    <hyperlink ref="B22" r:id="rId3" xr:uid="{FB56925B-0B62-44BA-927F-C2AC4732FB38}"/>
     <hyperlink ref="B4" r:id="rId4" xr:uid="{54D0229B-8293-478F-B28C-C2D9A0D38CA8}"/>
     <hyperlink ref="B7" r:id="rId5" xr:uid="{1486443F-40B3-4386-9E79-00457D4E63D8}"/>
     <hyperlink ref="B8" r:id="rId6" xr:uid="{61C7384B-50F0-4BBD-BF3D-155F05E6AF11}"/>
-    <hyperlink ref="B13" r:id="rId7" xr:uid="{2CE19BAF-EB88-42C3-B7DE-F8B738AF3D58}"/>
-    <hyperlink ref="B19" r:id="rId8" xr:uid="{6C4BF50A-C8CE-431A-9DF2-FA24A40FE5C4}"/>
+    <hyperlink ref="B14" r:id="rId7" xr:uid="{2CE19BAF-EB88-42C3-B7DE-F8B738AF3D58}"/>
+    <hyperlink ref="B20" r:id="rId8" xr:uid="{6C4BF50A-C8CE-431A-9DF2-FA24A40FE5C4}"/>
     <hyperlink ref="B3" r:id="rId9" xr:uid="{B903C235-2119-4640-8F19-A55E0B11DE36}"/>
-    <hyperlink ref="B16" r:id="rId10" xr:uid="{81F216F2-0FDA-4DBA-A975-5DEFAB9F0196}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{E6F99A8F-64E3-4A53-BDF6-5AA09ED63B83}"/>
-    <hyperlink ref="B11" r:id="rId12" xr:uid="{53A7D4AE-63EA-45E1-B664-AD57B74F8528}"/>
+    <hyperlink ref="B17" r:id="rId10" xr:uid="{81F216F2-0FDA-4DBA-A975-5DEFAB9F0196}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{E6F99A8F-64E3-4A53-BDF6-5AA09ED63B83}"/>
+    <hyperlink ref="B12" r:id="rId12" xr:uid="{53A7D4AE-63EA-45E1-B664-AD57B74F8528}"/>
     <hyperlink ref="B2" r:id="rId13" xr:uid="{A33A9F9D-F79F-4541-BAA5-7DFAE51479AC}"/>
     <hyperlink ref="B6" r:id="rId14" xr:uid="{436E6A2B-7251-4D2D-A8FA-0B2FF136CA1C}"/>
-    <hyperlink ref="B25" r:id="rId15" xr:uid="{0F2105CB-BF6F-4504-86C0-C6E5C69D7629}"/>
-    <hyperlink ref="B22" r:id="rId16" xr:uid="{4C1CB914-6529-4C3A-9ABD-2EA3A7D23E01}"/>
+    <hyperlink ref="B26" r:id="rId15" xr:uid="{0F2105CB-BF6F-4504-86C0-C6E5C69D7629}"/>
+    <hyperlink ref="B23" r:id="rId16" xr:uid="{4C1CB914-6529-4C3A-9ABD-2EA3A7D23E01}"/>
     <hyperlink ref="B5" r:id="rId17" xr:uid="{668CAE63-25B5-4184-BDB9-008B3ABAD465}"/>
-    <hyperlink ref="B23" r:id="rId18" xr:uid="{7F78273B-0909-4E46-979C-EA3A2A35FFED}"/>
-    <hyperlink ref="B20" r:id="rId19" xr:uid="{9E6CE64F-42BB-4349-8C52-4F786C099E9F}"/>
-    <hyperlink ref="B10" r:id="rId20" xr:uid="{E2CE4B0C-2C31-4101-924B-FA34C9B96D8B}"/>
-    <hyperlink ref="B9" r:id="rId21" xr:uid="{E5F7519E-1CFD-4EFE-8008-1DCF3D856628}"/>
-    <hyperlink ref="B15" r:id="rId22" xr:uid="{A74FC163-9C20-47DC-B816-E4216FC48078}"/>
-    <hyperlink ref="B17" r:id="rId23" xr:uid="{59755484-8087-4CE4-818B-F400662B180B}"/>
-    <hyperlink ref="B14" r:id="rId24" xr:uid="{6091812A-5BFD-454E-9BDF-021AE31D0735}"/>
+    <hyperlink ref="B24" r:id="rId18" xr:uid="{7F78273B-0909-4E46-979C-EA3A2A35FFED}"/>
+    <hyperlink ref="B21" r:id="rId19" xr:uid="{9E6CE64F-42BB-4349-8C52-4F786C099E9F}"/>
+    <hyperlink ref="B11" r:id="rId20" xr:uid="{E2CE4B0C-2C31-4101-924B-FA34C9B96D8B}"/>
+    <hyperlink ref="B10" r:id="rId21" xr:uid="{E5F7519E-1CFD-4EFE-8008-1DCF3D856628}"/>
+    <hyperlink ref="B16" r:id="rId22" xr:uid="{A74FC163-9C20-47DC-B816-E4216FC48078}"/>
+    <hyperlink ref="B18" r:id="rId23" xr:uid="{59755484-8087-4CE4-818B-F400662B180B}"/>
+    <hyperlink ref="B15" r:id="rId24" xr:uid="{6091812A-5BFD-454E-9BDF-021AE31D0735}"/>
+    <hyperlink ref="B9" r:id="rId25" xr:uid="{49F94D3E-7630-41F1-933B-7EFDA2E44919}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId25"/>
+  <pageSetup orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>